--- a/docs/assets/infraestructura/s1-e2-matriz-componentes-dimensionamiento.xlsx
+++ b/docs/assets/infraestructura/s1-e2-matriz-componentes-dimensionamiento.xlsx
@@ -516,7 +516,7 @@
     <col min="4" max="4" width="16.83203125" customWidth="1"/>
     <col min="5" max="5" width="59.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="54.83203125" customWidth="1"/>
+    <col min="7" max="7" width="59.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1252,7 +1252,7 @@
         <v>Crítica</v>
       </c>
       <c r="G32" t="str">
-        <v>Implementado (reglas corregidas sin publicar)</v>
+        <v>Implementado (reglas corregidas publicadas el 2026-10-24)</v>
       </c>
     </row>
     <row r="33">

--- a/docs/assets/infraestructura/s1-e2-matriz-componentes-dimensionamiento.xlsx
+++ b/docs/assets/infraestructura/s1-e2-matriz-componentes-dimensionamiento.xlsx
@@ -514,7 +514,7 @@
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
     <col min="3" max="3" width="31.83203125" customWidth="1"/>
     <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="59.83203125" customWidth="1"/>
+    <col min="5" max="5" width="60.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
     <col min="7" max="7" width="59.83203125" customWidth="1"/>
   </cols>
@@ -815,7 +815,7 @@
         <v>Alta</v>
       </c>
       <c r="G13" t="str">
-        <v>Diseñado (hoy en la PC local)</v>
+        <v>Diseñado (hoy en el VPS)</v>
       </c>
     </row>
     <row r="14">
@@ -1062,7 +1062,7 @@
         <v>Cómputo</v>
       </c>
       <c r="E24" t="str">
-        <v>Servidor del colegio y extremo VPN</v>
+        <v>Servidor del colegio, capa relacional de la academia (desde el 2026-10-24) y extremo VPN</v>
       </c>
       <c r="F24" t="str">
         <v>Crítica</v>
@@ -1352,7 +1352,7 @@
         <v>CD-36</v>
       </c>
       <c r="B37" t="str">
-        <v>PC local actual con PM2 (API, MySQL y analítica)</v>
+        <v>PC local con PM2 (entorno anterior de la capa)</v>
       </c>
       <c r="C37" t="str">
         <v>On-premise (actual)</v>
@@ -1361,13 +1361,13 @@
         <v>Cómputo</v>
       </c>
       <c r="E37" t="str">
-        <v>Servicio transitorio hasta VM-APP01</v>
+        <v>Desde el 2026-10-24 solo pruebas de restauración</v>
       </c>
       <c r="F37" t="str">
         <v>Media</v>
       </c>
       <c r="G37" t="str">
-        <v>Implementado (transitorio)</v>
+        <v>Retirado (2026-10-24): la capa corre en el VPS</v>
       </c>
     </row>
   </sheetData>
@@ -1867,8 +1867,8 @@
   <dimension ref="A1:D11"/>
   <cols>
     <col min="1" max="1" width="60.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="43.83203125" customWidth="1"/>
+    <col min="3" max="3" width="59.83203125" customWidth="1"/>
     <col min="4" max="4" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2017,13 +2017,13 @@
         <v>Capa de la academia (API Node, MySQL 8 y FastAPI)</v>
       </c>
       <c r="B11" t="str">
-        <v>≈ 600 (supuesto)</v>
+        <v>≈ 200 medidos (1,5 → 1,3 GiB disponibles)</v>
       </c>
       <c r="C11" t="str">
-        <v>Excluida del VPS</v>
+        <v>Alojada en el VPS desde el 2026-10-24 (desvío del diseño)</v>
       </c>
       <c r="D11" t="str">
-        <v>Se aloja on-premise en VM-APP01 (riesgo R-08)</v>
+        <v>free -h antes de instalar y con todo en marcha: 685 MiB usados y 1,3 GiB disponibles (manual de despliegue §9.0 y §9.4); MySQL con buffer de 128 MB y performance_schema desactivado; destino de diseño: VM-APP01 (riesgo R-08)</v>
       </c>
     </row>
   </sheetData>
@@ -2041,7 +2041,7 @@
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
     <col min="3" max="3" width="60.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" customWidth="1"/>
     <col min="5" max="5" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2291,13 +2291,13 @@
         <v>Uso real de RAM y disco del VPS</v>
       </c>
       <c r="C15" t="str">
-        <v>Ver presupuesto de RAM</v>
+        <v>1,9 GiB de RAM con 1,5 GiB disponibles y 28 GB libres antes de la capa de la academia; 1,3 GiB disponibles con ella en marcha</v>
       </c>
       <c r="D15" t="str">
-        <v>Supuesto a validar</v>
+        <v>Medido (2026-10-24)</v>
       </c>
       <c r="E15" t="str">
-        <v>free -m y df -h en el VPS</v>
+        <v>free -h y df -h en el VPS (manual de despliegue §9.0 y §9.4)</v>
       </c>
     </row>
   </sheetData>
@@ -2313,12 +2313,12 @@
   <dimension ref="A1:G11"/>
   <cols>
     <col min="1" max="1" width="45.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="2" max="2" width="32.83203125" customWidth="1"/>
     <col min="3" max="3" width="22.83203125" customWidth="1"/>
     <col min="4" max="4" width="48.83203125" customWidth="1"/>
     <col min="5" max="5" width="20.83203125" customWidth="1"/>
     <col min="6" max="6" width="60.83203125" customWidth="1"/>
-    <col min="7" max="7" width="17.83203125" customWidth="1"/>
+    <col min="7" max="7" width="34.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2418,7 +2418,7 @@
         <v>API de sincronización y MySQL</v>
       </c>
       <c r="B5" t="str">
-        <v>VM-APP01 (hoy PC local)</v>
+        <v>VM-APP01 (hoy VPS del colegio)</v>
       </c>
       <c r="C5" t="str">
         <v>Alta</v>
@@ -2430,10 +2430,10 @@
         <v>24 h</v>
       </c>
       <c r="F5" t="str">
-        <v>backup.js diario y restore.js; resincronización desde Firestore</v>
+        <v>backup.js diario (temporizador de systemd en el VPS) y restore.js; resincronización desde Firestore</v>
       </c>
       <c r="G5" t="str">
-        <v>REC-01 a REC-05</v>
+        <v>REC-01 a REC-05, REC-13 y REC-14</v>
       </c>
     </row>
     <row r="6">
@@ -2441,7 +2441,7 @@
         <v>Analítica</v>
       </c>
       <c r="B6" t="str">
-        <v>VM-APP01</v>
+        <v>VM-APP01 (hoy VPS del colegio)</v>
       </c>
       <c r="C6" t="str">
         <v>Baja</v>
